--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_weighted_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_weighted_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>4.03610751486715</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3.36709662825558</v>
+        <v>2.11484733447655</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>3.89727223830345</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>3.18816483121358</v>
+        <v>2.05900614329984</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>3.79760732829415</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>3.06003719180431</v>
+        <v>2.0218781807375</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>3.70732121608442</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2.94420874186689</v>
+        <v>1.98817278538656</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>3.58428793741545</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2.78675519806684</v>
+        <v>1.94212843851339</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>3.45814027872251</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2.62580134210985</v>
+        <v>1.89477553566606</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>3.40962308095765</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2.56403402688493</v>
+        <v>1.87652306297325</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>3.34873590107505</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>2.4866296184385</v>
+        <v>1.8535841734293</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>3.27069319121439</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>2.38760192536065</v>
+        <v>1.82412719158977</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>3.20407963521221</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>2.3032473358849</v>
+        <v>1.79893379299292</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>3.11501142672684</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>2.19071275854954</v>
+        <v>1.74215610721974</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>3.02355639691724</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>2.07547850630948</v>
+        <v>1.67374898052116</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>2.68948356621787</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1.66877790466321</v>
+        <v>1.41887551980316</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>2.53346191816271</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>1.4997173190957</v>
+        <v>1.31757468590096</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>2.39899511041129</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1.3545634625014</v>
+        <v>1.2245479265192</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>2.17114819382574</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>1.10990617548323</v>
+        <v>1.04397621447969</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>1.97644302944725</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.902305549909085</v>
+        <v>0.897280900504531</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>1.88892996456296</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.80949607513704</v>
+        <v>0.841985876915532</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>1.74999325634934</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.662862665096037</v>
+        <v>0.726626941295238</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>1.64669366348657</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.554463031703566</v>
+        <v>0.700583656559853</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>1.55293198602618</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.456581332667973</v>
+        <v>0.647193507679185</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>1.49156616696659</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.39280420987641</v>
+        <v>0.598736550546821</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>1.27939005563209</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.202741866576897</v>
+        <v>0.513090317295163</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>1.14894188207912</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.215571942407888</v>
+        <v>0.410242397896153</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>1.0214209431108</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.313015538171719</v>
+        <v>0.393177193477738</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>0.99250712184202</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.34409428480986</v>
+        <v>0.373867250741239</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>0.927364816751863</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.339911084382209</v>
+        <v>0.381447605402699</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>0.906222448414256</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.33714696903863</v>
+        <v>0.373834322527892</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>0.794176877451572</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.322366354042368</v>
+        <v>0.32928303647004</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>0.755148082521651</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.346769143101495</v>
+        <v>0.353146881539712</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>0.672593556631795</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.370081498757213</v>
+        <v>0.364225963464781</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>0.628953575722647</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.349988914035631</v>
+        <v>0.364467734614077</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>0.499168178633155</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.301820383211604</v>
+        <v>0.407717512619848</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>0.395452117595443</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.406460543151184</v>
+        <v>0.422388076685786</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>0.341204151788457</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.459097015935876</v>
+        <v>0.449214741737086</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.242440622472179</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.549167749442859</v>
+        <v>0.482359452296551</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.179198138333003</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.600249014253247</v>
+        <v>0.499080538035381</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.140834163465483</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.626347343116973</v>
+        <v>0.502256380393319</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.125795695017469</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.634793171334209</v>
+        <v>0.491768939073541</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.075605471012971</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.640848337269201</v>
+        <v>0.511278115057867</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.0688902294312126</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.621603586595882</v>
+        <v>0.488833105203925</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.0660110819171991</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.564576508719206</v>
+        <v>0.443170885772158</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.0641884962104147</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.523203813933296</v>
+        <v>0.407092048222411</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.0637027429342351</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.511146685434927</v>
+        <v>0.399571061250987</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.0627419148395091</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.472554195156401</v>
+        <v>0.38219626196625</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.060329457109403</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.304530847284521</v>
+        <v>0.294595350878217</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.059457487271234</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.190286728901167</v>
+        <v>0.270038246168362</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.0593252659524607</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.149324835199572</v>
+        <v>0.258579560299871</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.0592960803704308</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.121696816277876</v>
+        <v>0.247514394945301</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.0592993418768224</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.109570085323769</v>
+        <v>0.245600243080113</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.0606968014421656</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.0702457735328208</v>
+        <v>0.216478527823576</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.065681314098524</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.135288372204968</v>
+        <v>0.21174002894707</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.0671463489448622</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.15494628254646</v>
+        <v>0.204633707950902</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.0732799105801553</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.214451418685747</v>
+        <v>0.186948236123021</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.0786943021055174</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.241837202019891</v>
+        <v>0.192707076206804</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.0792350011763221</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.241547644366543</v>
+        <v>0.195718503023012</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>0.0792350011763221</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.241547644366543</v>
+        <v>0.195718503023012</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>0.0820777501245679</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.23980060564151</v>
+        <v>0.205678479876538</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>0.0832301518556622</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.238995592708783</v>
+        <v>0.209917226938953</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>0.0896171503445317</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.254910989315465</v>
+        <v>0.240056293255279</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>0.0907627025550999</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.260527969586351</v>
+        <v>0.245510273050714</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>0.105959770856604</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.31679702533015</v>
+        <v>0.274912967526749</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>0.108833299505261</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.324454022599148</v>
+        <v>0.281772657372352</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>0.118706718117383</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.33719540238282</v>
+        <v>0.308293016230143</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>0.128536193274882</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.337533597932255</v>
+        <v>0.319063852375943</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>0.143349853743461</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.329799320183324</v>
+        <v>0.308483203147802</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>0.155179197688957</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.318017070034512</v>
+        <v>0.287887594106148</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>0.16910669115703</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.299069657888591</v>
+        <v>0.290064213128773</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>0.195434069929176</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.251500571145364</v>
+        <v>0.295123313203915</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>0.216883953508594</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.203882623686623</v>
+        <v>0.290020351492716</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>0.251171327414275</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.141415889979737</v>
+        <v>0.284242187910615</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>0.272855035248911</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.120193411172062</v>
+        <v>0.295608477734185</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>0.299839676309389</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.119492469699868</v>
+        <v>0.295220759731193</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>0.314098753651326</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.147409765862679</v>
+        <v>0.291806757777517</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>0.325254959402188</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.169406200555853</v>
+        <v>0.297881727720982</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>0.336086443406276</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.182059758706678</v>
+        <v>0.293414916179359</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>0.3495223802567</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.19671104295821</v>
+        <v>0.288151594395929</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>0.361234008929042</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.238008914369529</v>
+        <v>0.305286344619839</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>0.379456904270322</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.238298938159714</v>
+        <v>0.362883941089748</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>0.455108081863847</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.414818216618278</v>
+        <v>0.438416575077686</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.474197837523964</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.472814291839061</v>
+        <v>0.492346909015075</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.574874745461984</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.685062890304329</v>
+        <v>0.757098690304911</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.637108818173934</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.911468999864148</v>
+        <v>0.895122342089843</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.642707503246536</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.932587896629596</v>
+        <v>0.895892142106406</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>0.698369711408851</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>1.14619030926156</v>
+        <v>0.897459628027489</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>0.760541757855618</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>1.39186186930797</v>
+        <v>1.05797522167</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>0.849914757139079</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>1.75626759744953</v>
+        <v>1.30642345831306</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>0.853634503584953</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>1.77169264091835</v>
+        <v>1.31065054706973</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>0.998261345043655</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>2.38524983486475</v>
+        <v>1.67912532101668</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>1.1581772838469</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>3.09019184997576</v>
+        <v>2.18790101693637</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>6.42834360733137</v>
+        <v>2.54263879906408</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
